--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.145.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.145.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.145.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.145.xlsx
@@ -423,17 +423,17 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” Lct the form be varied according</t>
+          <t>L114: suspicious token(s): NoTE (odd internal casing) :: NoTE.— Lct the form be varied according</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -611,28 +611,32 @@
           <t>L88: suspicious token(s): provisions0 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "provisions 0" vs "provisions0" :: provisions0</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” Lct the form be varied according</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,in the ------</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]138</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]138</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 138</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]138</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,in the ------</t>
+          <t>L19: punctuation artifact: double/multiple hyphen :: —,in the ------</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -678,16 +682,8 @@
           <t>L110: line starts with digit/letter garbage token | suspicious token(s): 1If (letter/digit mix) :: 1If upon</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: further relief ; pray subpenaÃ¦na.)</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”Let the form be varied according to circumstances.</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -762,7 +758,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -961,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1044,7 +1040,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
